--- a/real_estate_forms/047_property_listing_form--real_estate_forms.xlsx
+++ b/real_estate_forms/047_property_listing_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'residential',_'value':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Residential', 'value': 'residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'commercial',_'value':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Commercial', 'value': 'commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'for_sale',_'value':_'for_sale'}</t>
+          <t>for_sale</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'For Sale', 'value': 'for_sale'}</t>
+          <t>For Sale</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'for_rent',_'value':_'for_rent'}</t>
+          <t>for_rent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'For Rent', 'value': 'for_rent'}</t>
+          <t>For Rent</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'sold_out',_'value':_'sold_out'}</t>
+          <t>sold_out</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Sold Out', 'value': 'sold_out'}</t>
+          <t>Sold Out</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'lot',_'value':_'lot'}</t>
+          <t>lot</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Lot', 'value': 'lot'}</t>
+          <t>Lot</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'land',_'value':_'land'}</t>
+          <t>land</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Land', 'value': 'land'}</t>
+          <t>Land</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pool',_'value':_'pool'}</t>
+          <t>pool</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pool', 'value': 'pool'}</t>
+          <t>Pool</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'view',_'value':_'view'}</t>
+          <t>view</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'View', 'value': 'view'}</t>
+          <t>View</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'parking',_'value':_'parking'}</t>
+          <t>parking</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Parking', 'value': 'parking'}</t>
+          <t>Parking</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'fenced',_'value':_'fenced'}</t>
+          <t>fenced</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Fenced', 'value': 'fenced'}</t>
+          <t>Fenced</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'photos',_'value':_'photos'}</t>
+          <t>photos</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Photos', 'value': 'photos'}</t>
+          <t>Photos</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'videos',_'value':_'videos'}</t>
+          <t>videos</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Videos', 'value': 'videos'}</t>
+          <t>Videos</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'3d_tour',_'value':_'3d_tour'}</t>
+          <t>3d_tour</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '3D Tour', 'value': '3d_tour'}</t>
+          <t>3D Tour</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Jimmy', 'value': 'jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'jane',_'value':_'jane'}</t>
+          <t>jane</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Jane', 'value': 'jane'}</t>
+          <t>Jane</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Other', 'value': 'other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'city',_'value':_'city'}</t>
+          <t>city</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'City', 'value': 'city'}</t>
+          <t>City</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'state',_'value':_'state'}</t>
+          <t>state</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'State', 'value': 'state'}</t>
+          <t>State</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'county',_'value':_'county'}</t>
+          <t>county</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'County', 'value': 'county'}</t>
+          <t>County</t>
         </is>
       </c>
     </row>
